--- a/data/trans_camb/IP2003-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Edad-trans_camb.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,33</t>
+          <t>0,0; 12,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 3,28</t>
+          <t>-2,95; 3,23</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 4,86</t>
+          <t>-2,03; 4,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 6,55</t>
+          <t>-1,57; 6,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 4,47</t>
+          <t>-1,73; 4,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,26</t>
+          <t>-3,02; 3,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 6,58</t>
+          <t>-1,28; 6,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 2,95</t>
+          <t>-1,5; 2,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,69</t>
+          <t>-1,41; 3,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,41</t>
+          <t>-0,07; 5,17</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 109,63</t>
+          <t>-50,78; 106,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-40,63; 155,03</t>
+          <t>-36,27; 161,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 222,42</t>
+          <t>-30,9; 209,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,16; 162,69</t>
+          <t>-32,23; 166,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,81; 124,46</t>
+          <t>-52,42; 100,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,83; 239,07</t>
+          <t>-28,81; 228,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-28,26; 88,39</t>
+          <t>-27,0; 91,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 83,74</t>
+          <t>-27,6; 107,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 159,87</t>
+          <t>-8,04; 146,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 8,96</t>
+          <t>-8,04; 8,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,66; -1,75</t>
+          <t>-17,69; -1,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,93; -1,58</t>
+          <t>-18,48; -1,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 6,35</t>
+          <t>-8,98; 6,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,53; 4,24</t>
+          <t>-9,55; 5,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,41; -3,0</t>
+          <t>-17,35; -2,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 4,8</t>
+          <t>-6,39; 5,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,49; -0,63</t>
+          <t>-11,1; -0,16</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,31; -4,58</t>
+          <t>-15,59; -4,61</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 39,72</t>
+          <t>-24,65; 37,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,18; -6,84</t>
+          <t>-55,29; -7,9</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,89; -6,64</t>
+          <t>-58,46; -4,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,98; 38,27</t>
+          <t>-34,82; 38,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,82; 24,49</t>
+          <t>-36,86; 29,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,53; -17,2</t>
+          <t>-66,76; -11,93</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 21,98</t>
+          <t>-23,0; 24,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,35; -2,52</t>
+          <t>-39,67; -0,05</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,7; -21,8</t>
+          <t>-56,84; -20,92</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 6,33</t>
+          <t>-9,24; 6,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,52; -1,6</t>
+          <t>-16,61; -1,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 16,44</t>
+          <t>-18,48; 13,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 5,99</t>
+          <t>-8,9; 5,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 4,09</t>
+          <t>-10,12; 4,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 5,35</t>
+          <t>-12,71; 5,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,53; 3,65</t>
+          <t>-7,1; 4,07</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,71; -0,38</t>
+          <t>-11,81; -0,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,51; 5,69</t>
+          <t>-12,73; 6,91</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,22; 21,1</t>
+          <t>-25,12; 23,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-44,18; -5,65</t>
+          <t>-43,91; -5,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,99; 55,12</t>
+          <t>-51,14; 44,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 24,96</t>
+          <t>-28,59; 24,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-35,62; 17,09</t>
+          <t>-33,14; 20,87</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,5; 26,11</t>
+          <t>-43,18; 22,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-22,22; 12,99</t>
+          <t>-21,36; 14,93</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,32; -1,05</t>
+          <t>-34,44; -0,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,69; 20,13</t>
+          <t>-40,43; 24,31</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,52</t>
+          <t>-4,03; 2,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,84</t>
+          <t>-6,83; -0,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 12,81</t>
+          <t>-5,34; 11,46</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 2,14</t>
+          <t>-4,37; 1,69</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,46</t>
+          <t>-4,07; 1,9</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 4,84</t>
+          <t>-3,77; 4,42</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 1,42</t>
+          <t>-3,11; 1,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; -0,36</t>
+          <t>-4,94; -0,52</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 5,8</t>
+          <t>-3,31; 5,31</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 15,76</t>
+          <t>-21,07; 16,09</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-38,69; -5,21</t>
+          <t>-36,26; -5,29</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,52; 87,83</t>
+          <t>-28,94; 72,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 16,89</t>
+          <t>-27,57; 12,94</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,04; 11,82</t>
+          <t>-26,27; 13,91</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-23,7; 39,13</t>
+          <t>-24,52; 33,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 8,83</t>
+          <t>-18,82; 10,63</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,82; -1,89</t>
+          <t>-28,54; -3,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-19,52; 37,75</t>
+          <t>-20,26; 37,94</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Edad-trans_camb.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,85</t>
+          <t>0,0; 9,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 3,23</t>
+          <t>-3,04; 3,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 4,99</t>
+          <t>-2,1; 4,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 6,78</t>
+          <t>-1,39; 6,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 4,67</t>
+          <t>-1,64; 4,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 3,09</t>
+          <t>-2,94; 3,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 6,63</t>
+          <t>-1,21; 6,64</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 2,88</t>
+          <t>-1,4; 3,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 3,25</t>
+          <t>-1,64; 2,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,17</t>
+          <t>-0,26; 5,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-50,78; 106,94</t>
+          <t>-54,52; 99,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,27; 161,83</t>
+          <t>-38,2; 137,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 209,22</t>
+          <t>-27,84; 219,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-32,23; 166,7</t>
+          <t>-30,36; 196,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-52,42; 100,24</t>
+          <t>-50,38; 110,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-28,81; 228,39</t>
+          <t>-24,66; 224,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 91,24</t>
+          <t>-27,13; 86,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,6; 107,02</t>
+          <t>-30,63; 80,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 146,62</t>
+          <t>-6,01; 146,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 8,71</t>
+          <t>-8,32; 9,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,69; -1,98</t>
+          <t>-17,98; -1,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-18,48; -1,47</t>
+          <t>-17,8; -1,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 6,63</t>
+          <t>-10,08; 5,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,55; 5,05</t>
+          <t>-9,1; 5,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-17,35; -2,46</t>
+          <t>-16,86; -2,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,39; 5,29</t>
+          <t>-6,26; 4,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -0,16</t>
+          <t>-11,42; -0,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,59; -4,61</t>
+          <t>-15,67; -4,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-24,65; 37,97</t>
+          <t>-25,75; 40,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,29; -7,9</t>
+          <t>-54,9; -4,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-58,46; -4,43</t>
+          <t>-55,49; -3,61</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-34,82; 38,79</t>
+          <t>-38,12; 32,17</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-36,86; 29,31</t>
+          <t>-35,83; 34,18</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,76; -11,93</t>
+          <t>-64,89; -14,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 24,5</t>
+          <t>-23,26; 22,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -0,05</t>
+          <t>-41,09; -0,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-56,84; -20,92</t>
+          <t>-57,05; -19,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,24; 6,81</t>
+          <t>-9,12; 7,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,61; -1,43</t>
+          <t>-16,45; -0,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 13,32</t>
+          <t>-18,74; 16,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 5,43</t>
+          <t>-8,3; 6,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 4,9</t>
+          <t>-10,58; 4,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,71; 5,22</t>
+          <t>-12,47; 5,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,07</t>
+          <t>-6,3; 4,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,81; -0,5</t>
+          <t>-10,72; -0,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-12,73; 6,91</t>
+          <t>-13,6; 5,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-25,12; 23,87</t>
+          <t>-24,06; 23,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,91; -5,05</t>
+          <t>-43,83; -0,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,14; 44,42</t>
+          <t>-51,65; 57,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,59; 24,15</t>
+          <t>-27,04; 26,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,14; 20,87</t>
+          <t>-34,17; 18,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 22,11</t>
+          <t>-41,59; 24,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,36; 14,93</t>
+          <t>-19,05; 14,84</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-34,44; -0,61</t>
+          <t>-32,39; -1,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,43; 24,31</t>
+          <t>-41,42; 22,3</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 2,6</t>
+          <t>-4,01; 3,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -0,91</t>
+          <t>-7,21; -0,38</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 11,46</t>
+          <t>-5,4; 10,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 1,69</t>
+          <t>-3,82; 2,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 1,9</t>
+          <t>-4,34; 1,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 4,42</t>
+          <t>-3,83; 4,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 1,61</t>
+          <t>-3,09; 1,32</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; -0,52</t>
+          <t>-4,66; -0,26</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 5,31</t>
+          <t>-3,31; 6,28</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 16,09</t>
+          <t>-20,73; 19,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,26; -5,29</t>
+          <t>-37,41; -2,12</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-28,94; 72,96</t>
+          <t>-29,22; 75,68</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 12,94</t>
+          <t>-24,35; 16,78</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-26,27; 13,91</t>
+          <t>-27,87; 14,58</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-24,52; 33,69</t>
+          <t>-25,47; 35,92</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,82; 10,63</t>
+          <t>-18,07; 9,02</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,54; -3,38</t>
+          <t>-27,82; -1,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,26; 37,94</t>
+          <t>-20,18; 41,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2003-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP2003-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -634,24 +634,24 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0,99</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>2,33</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1,16</t>
+          <t>0,46</t>
         </is>
       </c>
     </row>
@@ -687,24 +687,24 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 5,06</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 9,63</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -717,7 +717,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
     </row>
@@ -740,22 +740,22 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,26</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,45</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,11</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>1,2</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,2</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,26</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,36</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,28</t>
+          <t>2,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,01</t>
+          <t>-1,58; 4,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 4,39</t>
+          <t>-3,09; 3,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 6,51</t>
+          <t>-1,18; 6,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 4,65</t>
+          <t>-3,19; 3,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 3,1</t>
+          <t>-2,29; 4,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 6,64</t>
+          <t>-1,06; 7,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,09</t>
+          <t>-1,51; 2,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 2,8</t>
+          <t>-1,65; 2,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 5,16</t>
+          <t>0,13; 5,87</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30,05%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>6,2%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57,67%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,52%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>26,8%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>49,24%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30,05%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,2%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,57%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>59,6%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-54,52; 99,78</t>
+          <t>-31,16; 162,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 137,46</t>
+          <t>-52,81; 124,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 219,33</t>
+          <t>-25,99; 245,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 196,0</t>
+          <t>-53,71; 109,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,38; 110,6</t>
+          <t>-40,63; 155,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 224,74</t>
+          <t>-25,26; 250,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-27,13; 86,68</t>
+          <t>-28,26; 88,39</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 80,02</t>
+          <t>-30,45; 83,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-6,01; 146,43</t>
+          <t>-1,82; 170,27</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,38</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-10,74</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,32</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-9,85</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-10,08</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,38</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-9,98</t>
+          <t>-11,46</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-10,18</t>
+          <t>-11,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,32; 9,36</t>
+          <t>-9,12; 6,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,98; -1,11</t>
+          <t>-9,53; 4,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,8; -1,43</t>
+          <t>-18,18; -4,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,08; 5,45</t>
+          <t>-8,49; 8,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 5,31</t>
+          <t>-17,66; -1,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,86; -2,83</t>
+          <t>-19,68; -3,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 4,98</t>
+          <t>-6,17; 4,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,42; -0,47</t>
+          <t>-11,49; -0,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-15,67; -4,45</t>
+          <t>-16,06; -6,02</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-7,72%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-10,95%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-49,49%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-35,76%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-36,6%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-7,72%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-10,95%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-45,99%</t>
+          <t>-41,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-41,59%</t>
+          <t>-45,47%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 40,27</t>
+          <t>-35,98; 38,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,9; -4,31</t>
+          <t>-36,82; 24,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-55,49; -3,61</t>
+          <t>-69,6; -22,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-38,12; 32,17</t>
+          <t>-26,27; 39,72</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,83; 34,18</t>
+          <t>-55,18; -6,84</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,89; -14,43</t>
+          <t>-61,69; -16,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 22,85</t>
+          <t>-22,44; 21,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-41,09; -0,59</t>
+          <t>-41,35; -2,52</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-57,05; -19,41</t>
+          <t>-59,1; -27,83</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,63</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-6,09</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-9,08</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-8,24</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,63</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,7</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-5,26</t>
+          <t>-15,36</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,75</t>
+          <t>-10,55</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 7,03</t>
+          <t>-8,46; 5,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,45; -0,73</t>
+          <t>-11,03; 4,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,74; 16,9</t>
+          <t>-12,96; 3,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 6,21</t>
+          <t>-9,61; 6,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 4,54</t>
+          <t>-16,52; -1,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,47; 5,45</t>
+          <t>-21,72; -7,81</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 4,15</t>
+          <t>-7,53; 3,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,72; -0,34</t>
+          <t>-10,71; -0,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-13,6; 5,36</t>
+          <t>-15,73; -4,99</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-5,98%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-9,87%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-22,29%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-3,72%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-26,36%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-23,92%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-5,98%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-9,87%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-19,25%</t>
+          <t>-44,58%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-21,94%</t>
+          <t>-34,27%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-24,06; 23,25</t>
+          <t>-27,29; 24,96</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-43,83; -0,72</t>
+          <t>-35,62; 17,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-51,65; 57,46</t>
+          <t>-43,06; 16,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,04; 26,08</t>
+          <t>-25,22; 21,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 18,8</t>
+          <t>-44,18; -5,65</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 24,47</t>
+          <t>-58,37; -26,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-19,05; 14,84</t>
+          <t>-22,22; 12,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-32,39; -1,22</t>
+          <t>-32,32; -1,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-41,42; 22,3</t>
+          <t>-47,9; -16,55</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,05</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,27</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,47</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-0,79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,06</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,05</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,27</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-3,46</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-1,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 3,06</t>
+          <t>-3,85; 2,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,21; -0,38</t>
+          <t>-4,39; 1,46</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 10,66</t>
+          <t>-3,82; 4,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 2,03</t>
+          <t>-4,18; 2,52</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 1,86</t>
+          <t>-7,21; -0,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 4,88</t>
+          <t>-7,09; 0,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,32</t>
+          <t>-3,22; 1,42</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,66; -0,26</t>
+          <t>-5,07; -0,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 6,28</t>
+          <t>-4,34; 0,86</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-7,37%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-8,93%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-3,3%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-4,47%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-23,1%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-1,9%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-7,37%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-8,93%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-1,02%</t>
+          <t>-19,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,84%</t>
+          <t>-12,13%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-20,73; 19,6</t>
+          <t>-25,17; 16,89</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,41; -2,12</t>
+          <t>-28,04; 11,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-29,22; 75,68</t>
+          <t>-24,67; 35,03</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,35; 16,78</t>
+          <t>-22,17; 15,76</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-27,87; 14,58</t>
+          <t>-38,69; -5,21</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,47; 35,92</t>
+          <t>-35,94; 2,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,07; 9,02</t>
+          <t>-19,28; 8,83</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-27,82; -1,92</t>
+          <t>-28,82; -1,89</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 41,37</t>
+          <t>-25,61; 6,02</t>
         </is>
       </c>
     </row>
